--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_ER다이어그램.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_ER다이어그램.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\HAYUL\eclipse\ShoppingMall\tmp\프로젝트 제출양식\2. 프로젝트 결과 보고서\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -98,37 +98,54 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:colOff>104775</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>77680</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>105829</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2"/>
+        <xdr:cNvPr id="4" name="그림 3" descr="C:\Users\admin\Desktop\HAYUL\eclipse\ShoppingMall\tmp\프로젝트 제출양식\2. 프로젝트 결과 보고서\ER다이어그램.png"/>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="76200" y="304800"/>
-          <a:ext cx="10602805" cy="7554379"/>
+          <a:off x="104775" y="266700"/>
+          <a:ext cx="10448925" cy="7524750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
